--- a/data/compare/do-ls-media-confidence.xlsx
+++ b/data/compare/do-ls-media-confidence.xlsx
@@ -34819,7 +34819,9 @@
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="65.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
